--- a/results/job_matches_2026-06-30.xlsx
+++ b/results/job_matches_2026-06-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS SysOp Admin/DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Neubus, Inc.</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,77 +696,77 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45e55bba1cdc0f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c9fc4b01a8878948</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Integrations Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diversify</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61dfb2e97bef5956</t>
+          <t>https://www.indeed.com/viewjob?jk=de1fca8ed87b85de</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data and Insight Analyst</t>
+          <t>AWS SysOp Admin/DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Neubus, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cece0455bb6da18d</t>
+          <t>https://www.indeed.com/viewjob?jk=b45e55bba1cdc0f9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer - GCP</t>
+          <t>Sr. Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Data Sherpas</t>
+          <t>Diversify</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, Scala, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212dc5034cb8bca8</t>
+          <t>https://www.indeed.com/viewjob?jk=61dfb2e97bef5956</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Big Data &amp; MCP, Data Foundations</t>
+          <t>Data and Insight Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Databricks, Hadoop, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e6bda7c4edc743</t>
+          <t>https://www.indeed.com/viewjob?jk=cece0455bb6da18d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Big Data &amp; MCP, Data Foundations</t>
+          <t>Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>The Data Sherpas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c603d89b037c27ac</t>
+          <t>https://www.indeed.com/viewjob?jk=212dc5034cb8bca8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Databricks Engineer and Architect</t>
+          <t>Senior Software Engineer- Big Data &amp; MCP, Data Foundations</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f0ddbe29bf07cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=12e6bda7c4edc743</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Senior Software Engineer- Big Data &amp; MCP, Data Foundations</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36e8e54920f0198</t>
+          <t>https://www.indeed.com/viewjob?jk=c603d89b037c27ac</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Databricks Engineer and Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03116dd5f77c4a08</t>
+          <t>https://www.indeed.com/viewjob?jk=5f0ddbe29bf07cc0</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca581db51f25003</t>
+          <t>https://www.indeed.com/viewjob?jk=b36e8e54920f0198</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III - ATI</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a9b04ee6e058585</t>
+          <t>https://www.indeed.com/viewjob?jk=03116dd5f77c4a08</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea10b210ba9e582</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca581db51f25003</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Fullstack Developer_Tempe, AZ</t>
+          <t>Software Engineer III - ATI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ccdf3f7c3217993</t>
+          <t>https://www.indeed.com/viewjob?jk=8a9b04ee6e058585</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Engineer, DevOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3933dfeda45c057</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea10b210ba9e582</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java &amp; AWS)</t>
+          <t>Fullstack Developer_Tempe, AZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Diversified Services Network, Inc.</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=960399573e934589</t>
+          <t>https://www.indeed.com/viewjob?jk=3ccdf3f7c3217993</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java &amp; AWS)</t>
+          <t>Senior Engineer, DevOps</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Diversified Services Network, Inc.</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51349eeea9315e96</t>
+          <t>https://www.indeed.com/viewjob?jk=d3933dfeda45c057</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS Software Engineer III-ETL/AI</t>
+          <t>Senior Software Engineer (Java &amp; AWS)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Diversified Services Network, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2de7adcc27fce6</t>
+          <t>https://www.indeed.com/viewjob?jk=960399573e934589</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
+          <t>Senior Software Engineer (Java &amp; AWS)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>Diversified Services Network, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c44ee92aa2c8400</t>
+          <t>https://www.indeed.com/viewjob?jk=51349eeea9315e96</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Software Engineer III-ETL/AI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Avaya</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hive, Spark, PySpark, Scala, ETL, ELT, Power BI, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626f550b7d7b1c09</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2de7adcc27fce6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5f1d848e75885</t>
+          <t>https://www.indeed.com/viewjob?jk=5c44ee92aa2c8400</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Forward Deployment Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Avaya</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>Azure, Databricks, Hive, Spark, PySpark, Scala, ETL, ELT, Power BI, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea91a33e0a092959</t>
+          <t>https://www.indeed.com/viewjob?jk=626f550b7d7b1c09</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75cb5876ca6eeca</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5f1d848e75885</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Platform Architect</t>
+          <t>AI Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Clark Construction</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4607a264c3f31959</t>
+          <t>https://www.indeed.com/viewjob?jk=ea91a33e0a092959</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ML Ops Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Circadia Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Spark, Dask, Snowflake, MLOps, MLflow, CI/CD</t>
+          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b91c752a8c427fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=a75cb5876ca6eeca</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III - Visual AI Technology</t>
+          <t>AI Native Builder</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bb194dac269cfc4</t>
+          <t>https://www.indeed.com/viewjob?jk=d734e7ef9a655ae9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer/Architect - MS Fabric</t>
+          <t>AI Native Builder</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1567,11 +1567,11 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>EMR, RDS, Data Factory, Medallion Architecture, Dataflow, Hadoop, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baea501e7691a719</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebf4addde4aec8c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Associate Data Engineer / Data Engineer II / Senior Data Engineer (REMOTE)</t>
+          <t>AI Native Builder</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1602,11 +1602,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=665858153a76bc87</t>
+          <t>https://www.indeed.com/viewjob?jk=64c15efcfbb29edc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Databricks Platform &amp; Data Engineer</t>
+          <t>Senior Data Platform Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Clark Construction</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4b537ec115b25d9</t>
+          <t>https://www.indeed.com/viewjob?jk=4607a264c3f31959</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure Databricks, Spark, PySpark, Scala)</t>
+          <t>ML Ops Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>Circadia Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Spark, Dask, Snowflake, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d65dc21087a459</t>
+          <t>https://www.indeed.com/viewjob?jk=b91c752a8c427fd0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer I</t>
+          <t>Software Engineer III - Visual AI Technology</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f53c7c2bf6f1f5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=2bb194dac269cfc4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5703940eacfe4257</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb2133b885b233e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala, Spark</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fdf8e05e3832326</t>
+          <t>https://www.indeed.com/viewjob?jk=65c09af802c5ffa3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>Data Engineer/Architect - MS Fabric</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>EMR, RDS, Data Factory, Medallion Architecture, Dataflow, Hadoop, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28f7c9f9313edca</t>
+          <t>https://www.indeed.com/viewjob?jk=baea501e7691a719</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>Associate Data Engineer / Data Engineer II / Senior Data Engineer (REMOTE)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1655be98963b6d30</t>
+          <t>https://www.indeed.com/viewjob?jk=665858153a76bc87</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>Databricks Platform &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57dce62ea127658</t>
+          <t>https://www.indeed.com/viewjob?jk=f4b537ec115b25d9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Data Engineer (Azure Databricks, Spark, PySpark, Scala)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Creve Coeur, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fed8aee2bab65bb</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d65dc21087a459</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Specialist - Software Development &amp; Engineering</t>
+          <t>NLM Cloud Engineer I</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4a561dc1cddafc</t>
+          <t>https://www.indeed.com/viewjob?jk=f53c7c2bf6f1f5a7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf9b523ed48e61a</t>
+          <t>https://www.indeed.com/viewjob?jk=5703940eacfe4257</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Scala Engineer</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Diversified Services Network, Inc.</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99b1c920fa5438bf</t>
+          <t>https://www.indeed.com/viewjob?jk=3fdf8e05e3832326</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Austin, TX - 2373630</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, Data Modeling, Splunk</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ecbcebb77acdc85</t>
+          <t>https://www.indeed.com/viewjob?jk=e28f7c9f9313edca</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fracht Group</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa96d3d36ceb7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=1655be98963b6d30</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2490431387959f09</t>
+          <t>https://www.indeed.com/viewjob?jk=d57dce62ea127658</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>Creve Coeur, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df0b13a3eb9c3062</t>
+          <t>https://www.indeed.com/viewjob?jk=3fed8aee2bab65bb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
+          <t>Specialist - Software Development &amp; Engineering</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbc7c313d9e51ca</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4a561dc1cddafc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0ead42f0db52dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=baf9b523ed48e61a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Scala Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Diversified Services Network, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac49aa80fd785089</t>
+          <t>https://www.indeed.com/viewjob?jk=99b1c920fa5438bf</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ML Search Engineer</t>
+          <t>Senior Software Engineer - Austin, TX - 2373630</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3eed5895ede4859</t>
+          <t>https://www.indeed.com/viewjob?jk=5ecbcebb77acdc85</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Fracht Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Talend, dbt</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95668eacef5ebd13</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa96d3d36ceb7ae</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Nashua, NH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20fc46279f198efe</t>
+          <t>https://www.indeed.com/viewjob?jk=2490431387959f09</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Nashua, NH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bec039b9620a5fef</t>
+          <t>https://www.indeed.com/viewjob?jk=df0b13a3eb9c3062</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48eb68de5366b63</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbc7c313d9e51ca</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Union City, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212a79337c567fc4</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d63ab0e4452de4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3048911b0454e84c</t>
+          <t>https://www.indeed.com/viewjob?jk=a0ead42f0db52dd0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Blob Storage, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02430a3484af15a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ac49aa80fd785089</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ML Search Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Azure, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a31d611f67e9e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3eed5895ede4859</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer - 2373611</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Jenkins, GitHub Actions</t>
+          <t>RDS, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e4cfd29eb8d796</t>
+          <t>https://www.indeed.com/viewjob?jk=95668eacef5ebd13</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0f3ea5b712aaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=20fc46279f198efe</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ETL/Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JCTM</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Informatica PowerCenter, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b5e94eddb1f9ba</t>
+          <t>https://www.indeed.com/viewjob?jk=bec039b9620a5fef</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, PostgreSQL, MySQL, Cassandra, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,102 +2736,102 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33da34be38b547b0</t>
+          <t>https://www.indeed.com/viewjob?jk=c48eb68de5366b63</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Intellivo</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a247e4c9f8838e</t>
+          <t>https://www.indeed.com/viewjob?jk=212a79337c567fc4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>INFORMATION SYSTEMS OFFICER, P3</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>United Nations</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab00abb249e3052</t>
+          <t>https://www.indeed.com/viewjob?jk=3048911b0454e84c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Associate Dir, Full Stack Data Scientist</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5df2a862bf9db8</t>
+          <t>https://www.indeed.com/viewjob?jk=02430a3484af15a3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Azure, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f5d55a58f8c38c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a31d611f67e9e2c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - 2373611</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>APLOMB Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New Boston, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=021284abbf4c58c0</t>
+          <t>https://www.indeed.com/viewjob?jk=54e4cfd29eb8d796</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a297ffaf533cd380</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0f3ea5b712aaf6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer (Agency Temp)</t>
+          <t>ETL/Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>JCTM</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Informatica PowerCenter, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ec69ba27334413b</t>
+          <t>https://www.indeed.com/viewjob?jk=84b5e94eddb1f9ba</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Trulieve</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, GCP, Scala, PostgreSQL, MySQL, Cassandra, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,102 +3016,102 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2502fbaa4654c499</t>
+          <t>https://www.indeed.com/viewjob?jk=33da34be38b547b0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Intellivo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, DynamoDB, Splunk, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9712b962bea6680</t>
+          <t>https://www.indeed.com/viewjob?jk=03a247e4c9f8838e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>INFORMATION SYSTEMS OFFICER, P3</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JCTM</t>
+          <t>United Nations</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1d90a9441d225d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab00abb249e3052</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Solutions Architect II - Omnichannel</t>
+          <t>Associate Dir, Full Stack Data Scientist</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51e91e41bcce9db6</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5df2a862bf9db8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
+          <t>https://www.indeed.com/viewjob?jk=92f5d55a58f8c38c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New Boston, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=602b89794c6d97b1</t>
+          <t>https://www.indeed.com/viewjob?jk=021284abbf4c58c0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Full Stack, Data &amp; Analytics Engineer (Agency Temp)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a86f04695064d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=1ec69ba27334413b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Database Engineer (contract)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Trulieve</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bbb3ea9ee7ee707</t>
+          <t>https://www.indeed.com/viewjob?jk=2502fbaa4654c499</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Ansible Automation Platform / Hybrid Cloud)</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DAS Federal</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50a892c497ffe06</t>
+          <t>https://www.indeed.com/viewjob?jk=f587f9ae6e2cdaae</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - APEX</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, DynamoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=533c4d256ae9eac9</t>
+          <t>https://www.indeed.com/viewjob?jk=a9712b962bea6680</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer, Jersey City, NJ - Onsite | In-person presence is mandatory</t>
+          <t>Sr. Database Administrator</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>American Credit Acceptance</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, IAM, RDS, Scala, Snowflake, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b357357f3cb8f80</t>
+          <t>https://www.indeed.com/viewjob?jk=7e55ba17244aa18c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Search Engineer</t>
+          <t>Solutions Architect II - Omnichannel</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b805c6c3ef2ef74</t>
+          <t>https://www.indeed.com/viewjob?jk=51e91e41bcce9db6</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Intern - Full Stack Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Rad Cube LLC</t>
+          <t>JCTM</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,19 +3436,19 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceebe7f570acd23b</t>
+          <t>https://www.indeed.com/viewjob?jk=0f1d90a9441d225d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Coverys</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3457,11 +3457,11 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c259b85236c51107</t>
+          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073dcbe12166b408</t>
+          <t>https://www.indeed.com/viewjob?jk=602b89794c6d97b1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5283a1c7f91253d8</t>
+          <t>https://www.indeed.com/viewjob?jk=1a86f04695064d5c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Associate Actuary</t>
+          <t>Database Engineer (contract)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2413f123744bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=7bbb3ea9ee7ee707</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Associate Actuary</t>
+          <t>Senior Systems Engineer (Ansible Automation Platform / Hybrid Cloud)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>DAS Federal</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e40dedeb41804c</t>
+          <t>https://www.indeed.com/viewjob?jk=c50a892c497ffe06</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data and AI Platform Engineer</t>
+          <t>Search Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JELLYFISH</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Data Modeling, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b805c6c3ef2ef74</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdbca4cb9ae66f3</t>
+          <t>https://www.indeed.com/viewjob?jk=073dcbe12166b408</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2bbd584cafb766</t>
+          <t>https://www.indeed.com/viewjob?jk=5283a1c7f91253d8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Actuary</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f49ef023c8c96de</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2413f123744bc5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Associate Actuary</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e7d8a3a432eba9</t>
+          <t>https://www.indeed.com/viewjob?jk=45e40dedeb41804c</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>JELLYFISH</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Data Modeling, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,67 +3821,67 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf46770fd8ff6a55</t>
+          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>Intern - Full Stack Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>Rad Cube LLC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e8a0f3adb10969c</t>
+          <t>https://www.indeed.com/viewjob?jk=ceebe7f570acd23b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Coverys</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d641f8b88bb4c</t>
+          <t>https://www.indeed.com/viewjob?jk=c259b85236c51107</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PostgreSQL, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c582c80db561b</t>
+          <t>https://www.indeed.com/viewjob?jk=af72bf959cb85028</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr Automation Engineer Sales</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Raya Workforce</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Woodstock, VT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21e43ea584d339bf</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdbca4cb9ae66f3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer - Java and Spring WebFlux</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, CI/CD, Maven, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd37326d3fa0289f</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2bbd584cafb766</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92021aa8ff2e1919</t>
+          <t>https://www.indeed.com/viewjob?jk=5f49ef023c8c96de</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e05275f5681930</t>
+          <t>https://www.indeed.com/viewjob?jk=68e7d8a3a432eba9</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>ZENO Group</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,29 +4091,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c6a7cf5bcefcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=bf46770fd8ff6a55</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Internally Deployed Products</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ClickUp</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, GCP, BigQuery, ETL, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb34b68319c8362</t>
+          <t>https://www.indeed.com/viewjob?jk=2e8a0f3adb10969c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796a5092268ae3dc</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d641f8b88bb4c</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Spark, PostgreSQL, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99dcfa53429fedf3</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c582c80db561b</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CADRE GOVERNMENT SOLUTIONS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Kafka, Kafka Connect, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a874a7bc98d4c6bb</t>
+          <t>https://www.indeed.com/viewjob?jk=ebfe3b1f1e233a71</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - US</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GreenBox Capital</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0eba562e0eef18</t>
+          <t>https://www.indeed.com/viewjob?jk=92021aa8ff2e1919</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2373638</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,15 +4301,295 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74e05275f5681930</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17c6a7cf5bcefcd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Internally Deployed Products</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ClickUp</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, GCP, BigQuery, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7eb34b68319c8362</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - US</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>GreenBox Capital</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d0eba562e0eef18</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=796a5092268ae3dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99dcfa53429fedf3</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Kafka Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CADRE GOVERNMENT SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Scala, Kafka, Kafka Connect, ETL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a874a7bc98d4c6bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Sr Automation Engineer Sales</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Raya Workforce</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Woodstock, VT, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21e43ea584d339bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - 2373638</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
           <t>Azure, Synapse Analytics, Scala, SQL Server, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=333af030098f9b44</t>
         </is>

--- a/results/job_matches_2026-06-30.xlsx
+++ b/results/job_matches_2026-06-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III - ATI</t>
+          <t>Senior IT Big Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a9b04ee6e058585</t>
+          <t>https://www.indeed.com/viewjob?jk=805d9159d3aff63f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea10b210ba9e582</t>
+          <t>https://www.indeed.com/viewjob?jk=8020391c43706e33</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fullstack Developer_Tempe, AZ</t>
+          <t>Software Engineer III - ATI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ccdf3f7c3217993</t>
+          <t>https://www.indeed.com/viewjob?jk=8a9b04ee6e058585</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Engineer, DevOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3933dfeda45c057</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea10b210ba9e582</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java &amp; AWS)</t>
+          <t>Fullstack Developer_Tempe, AZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Diversified Services Network, Inc.</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=960399573e934589</t>
+          <t>https://www.indeed.com/viewjob?jk=3ccdf3f7c3217993</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java &amp; AWS)</t>
+          <t>Senior Engineer, DevOps</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Diversified Services Network, Inc.</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51349eeea9315e96</t>
+          <t>https://www.indeed.com/viewjob?jk=d3933dfeda45c057</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Software Engineer III-ETL/AI</t>
+          <t>Senior Software Engineer (Java &amp; AWS)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Diversified Services Network, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2de7adcc27fce6</t>
+          <t>https://www.indeed.com/viewjob?jk=960399573e934589</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
+          <t>Senior Software Engineer (Java &amp; AWS)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>Diversified Services Network, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c44ee92aa2c8400</t>
+          <t>https://www.indeed.com/viewjob?jk=51349eeea9315e96</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Software Engineer III-ETL/AI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Avaya</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hive, Spark, PySpark, Scala, ETL, ELT, Power BI, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626f550b7d7b1c09</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2de7adcc27fce6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5f1d848e75885</t>
+          <t>https://www.indeed.com/viewjob?jk=5c44ee92aa2c8400</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Forward Deployment Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Avaya</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>Azure, Databricks, Hive, Spark, PySpark, Scala, ETL, ELT, Power BI, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea91a33e0a092959</t>
+          <t>https://www.indeed.com/viewjob?jk=626f550b7d7b1c09</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Software Engineer, Data (L1)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75cb5876ca6eeca</t>
+          <t>https://www.indeed.com/viewjob?jk=de33f3f460768669</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Native Builder</t>
+          <t>Software Engineer, Data (L1)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d734e7ef9a655ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=5a58fca26aa0b565</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Native Builder</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebf4addde4aec8c</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5f1d848e75885</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Native Builder</t>
+          <t>AI Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c15efcfbb29edc</t>
+          <t>https://www.indeed.com/viewjob?jk=ea91a33e0a092959</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Platform Architect</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Clark Construction</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4607a264c3f31959</t>
+          <t>https://www.indeed.com/viewjob?jk=a75cb5876ca6eeca</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ML Ops Engineer</t>
+          <t>Senior Data Platform Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Circadia Health</t>
+          <t>Clark Construction</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Spark, Dask, Snowflake, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b91c752a8c427fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=4607a264c3f31959</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III - Visual AI Technology</t>
+          <t>ML Ops Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Circadia Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Spark, Dask, Snowflake, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bb194dac269cfc4</t>
+          <t>https://www.indeed.com/viewjob?jk=b91c752a8c427fd0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - Visual AI Technology</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>North Andover, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb2133b885b233e</t>
+          <t>https://www.indeed.com/viewjob?jk=2bb194dac269cfc4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>North Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala, Spark</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c09af802c5ffa3</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb2133b885b233e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer/Architect - MS Fabric</t>
+          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>EMR, RDS, Data Factory, Medallion Architecture, Dataflow, Hadoop, Spark, PySpark, Scala, Data Modeling</t>
+          <t>Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala, Spark</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,19 +1826,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baea501e7691a719</t>
+          <t>https://www.indeed.com/viewjob?jk=65c09af802c5ffa3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Associate Data Engineer / Data Engineer II / Senior Data Engineer (REMOTE)</t>
+          <t>Data Engineer/Architect - MS Fabric</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>EMR, RDS, Data Factory, Medallion Architecture, Dataflow, Hadoop, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=665858153a76bc87</t>
+          <t>https://www.indeed.com/viewjob?jk=baea501e7691a719</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Databricks Platform &amp; Data Engineer</t>
+          <t>Data Engineer III, Development</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4b537ec115b25d9</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f5ff112c1e4fbb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure Databricks, Spark, PySpark, Scala)</t>
+          <t>Associate Data Engineer / Data Engineer II / Senior Data Engineer (REMOTE)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d65dc21087a459</t>
+          <t>https://www.indeed.com/viewjob?jk=665858153a76bc87</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer I</t>
+          <t>Databricks Platform &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f53c7c2bf6f1f5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=f4b537ec115b25d9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>NLM Cloud Engineer I</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5703940eacfe4257</t>
+          <t>https://www.indeed.com/viewjob?jk=f53c7c2bf6f1f5a7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Creve Coeur, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fdf8e05e3832326</t>
+          <t>https://www.indeed.com/viewjob?jk=3fed8aee2bab65bb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>Specialist - Software Development &amp; Engineering</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28f7c9f9313edca</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4a561dc1cddafc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1655be98963b6d30</t>
+          <t>https://www.indeed.com/viewjob?jk=baf9b523ed48e61a</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57dce62ea127658</t>
+          <t>https://www.indeed.com/viewjob?jk=5703940eacfe4257</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Creve Coeur, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fed8aee2bab65bb</t>
+          <t>https://www.indeed.com/viewjob?jk=3fdf8e05e3832326</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Specialist - Software Development &amp; Engineering</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4a561dc1cddafc</t>
+          <t>https://www.indeed.com/viewjob?jk=e28f7c9f9313edca</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf9b523ed48e61a</t>
+          <t>https://www.indeed.com/viewjob?jk=1655be98963b6d30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Scala Engineer</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Diversified Services Network, Inc.</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99b1c920fa5438bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d57dce62ea127658</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Databricks, Blob Storage, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0ead42f0db52dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=ac49aa80fd785089</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac49aa80fd785089</t>
+          <t>https://www.indeed.com/viewjob?jk=a0ead42f0db52dd0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ML Search Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3eed5895ede4859</t>
+          <t>https://www.indeed.com/viewjob?jk=95668eacef5ebd13</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Talend, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95668eacef5ebd13</t>
+          <t>https://www.indeed.com/viewjob?jk=20fc46279f198efe</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20fc46279f198efe</t>
+          <t>https://www.indeed.com/viewjob?jk=bec039b9620a5fef</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bec039b9620a5fef</t>
+          <t>https://www.indeed.com/viewjob?jk=c48eb68de5366b63</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48eb68de5366b63</t>
+          <t>https://www.indeed.com/viewjob?jk=212a79337c567fc4</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212a79337c567fc4</t>
+          <t>https://www.indeed.com/viewjob?jk=3048911b0454e84c</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3048911b0454e84c</t>
+          <t>https://www.indeed.com/viewjob?jk=02430a3484af15a3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>ML Search Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02430a3484af15a3</t>
+          <t>https://www.indeed.com/viewjob?jk=f3eed5895ede4859</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>MLOps Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0f3ea5b712aaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=dae99e1ea457637a</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Architect II - Omnichannel</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, DynamoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9712b962bea6680</t>
+          <t>https://www.indeed.com/viewjob?jk=51e91e41bcce9db6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Database Administrator</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>American Credit Acceptance</t>
+          <t>JCTM</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Scala, Snowflake, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e55ba17244aa18c</t>
+          <t>https://www.indeed.com/viewjob?jk=0f1d90a9441d225d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Solutions Architect II - Omnichannel</t>
+          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51e91e41bcce9db6</t>
+          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JCTM</t>
+          <t>Entiovi Technologies Private Limited</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bengal, IN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,42 +3426,42 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1d90a9441d225d</t>
+          <t>https://www.indeed.com/viewjob?jk=f89dc1b57a628321</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
+          <t>https://www.indeed.com/viewjob?jk=602b89794c6d97b1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=602b89794c6d97b1</t>
+          <t>https://www.indeed.com/viewjob?jk=1a86f04695064d5c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Database Engineer (contract)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a86f04695064d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=7bbb3ea9ee7ee707</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Database Engineer (contract)</t>
+          <t>Senior Systems Engineer (Ansible Automation Platform / Hybrid Cloud)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>DAS Federal</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bbb3ea9ee7ee707</t>
+          <t>https://www.indeed.com/viewjob?jk=c50a892c497ffe06</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Ansible Automation Platform / Hybrid Cloud)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DAS Federal</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50a892c497ffe06</t>
+          <t>https://www.indeed.com/viewjob?jk=073dcbe12166b408</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Search Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b805c6c3ef2ef74</t>
+          <t>https://www.indeed.com/viewjob?jk=5283a1c7f91253d8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Actuary</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073dcbe12166b408</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2413f123744bc5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Actuary</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5283a1c7f91253d8</t>
+          <t>https://www.indeed.com/viewjob?jk=45e40dedeb41804c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Associate Actuary</t>
+          <t>Senior Data and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>JELLYFISH</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Data Modeling, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2413f123744bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Associate Actuary</t>
+          <t>Intern - Full Stack Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>Rad Cube LLC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e40dedeb41804c</t>
+          <t>https://www.indeed.com/viewjob?jk=ceebe7f570acd23b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data and AI Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JELLYFISH</t>
+          <t>Coverys</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Data Modeling, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
+          <t>https://www.indeed.com/viewjob?jk=c259b85236c51107</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Intern - Full Stack Developer</t>
+          <t>Search Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Rad Cube LLC</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceebe7f570acd23b</t>
+          <t>https://www.indeed.com/viewjob?jk=1b805c6c3ef2ef74</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Coverys</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c259b85236c51107</t>
+          <t>https://www.indeed.com/viewjob?jk=af72bf959cb85028</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af72bf959cb85028</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdbca4cb9ae66f3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdbca4cb9ae66f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2bbd584cafb766</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2bbd584cafb766</t>
+          <t>https://www.indeed.com/viewjob?jk=5f49ef023c8c96de</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f49ef023c8c96de</t>
+          <t>https://www.indeed.com/viewjob?jk=68e7d8a3a432eba9</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>ZENO Group</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e7d8a3a432eba9</t>
+          <t>https://www.indeed.com/viewjob?jk=bf46770fd8ff6a55</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer, Data &amp; AI</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf46770fd8ff6a55</t>
+          <t>https://www.indeed.com/viewjob?jk=f70e3e5b69eb2b62</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e8a0f3adb10969c</t>
+          <t>https://www.indeed.com/viewjob?jk=92021aa8ff2e1919</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d641f8b88bb4c</t>
+          <t>https://www.indeed.com/viewjob?jk=74e05275f5681930</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PostgreSQL, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c582c80db561b</t>
+          <t>https://www.indeed.com/viewjob?jk=17c6a7cf5bcefcd6</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, PostgreSQL, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebfe3b1f1e233a71</t>
+          <t>https://www.indeed.com/viewjob?jk=2e8a0f3adb10969c</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92021aa8ff2e1919</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d641f8b88bb4c</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Backend Engineer - US</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>GreenBox Capital</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e05275f5681930</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0eba562e0eef18</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c6a7cf5bcefcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=796a5092268ae3dc</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Internally Deployed Products</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ClickUp</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, GCP, BigQuery, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb34b68319c8362</t>
+          <t>https://www.indeed.com/viewjob?jk=99dcfa53429fedf3</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - US</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>GreenBox Capital</t>
+          <t>CADRE GOVERNMENT SOLUTIONS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, RDS, Scala, Kafka, Kafka Connect, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0eba562e0eef18</t>
+          <t>https://www.indeed.com/viewjob?jk=a874a7bc98d4c6bb</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Sr Automation Engineer Sales</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Raya Workforce</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796a5092268ae3dc</t>
+          <t>https://www.indeed.com/viewjob?jk=21e43ea584d339bf</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Spark, PostgreSQL, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99dcfa53429fedf3</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c582c80db561b</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Senior Software Engineer - 2373638</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CADRE GOVERNMENT SOLUTIONS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Kafka, Kafka Connect, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Synapse Analytics, Scala, SQL Server, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a874a7bc98d4c6bb</t>
+          <t>https://www.indeed.com/viewjob?jk=333af030098f9b44</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr Automation Engineer Sales</t>
+          <t>Senior Software Engineer, Internally Deployed Products</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Raya Workforce</t>
+          <t>ClickUp</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Woodstock, VT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, GCP, BigQuery, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,42 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21e43ea584d339bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - 2373638</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Azure, Synapse Analytics, Scala, SQL Server, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=333af030098f9b44</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb34b68319c8362</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-30.xlsx
+++ b/results/job_matches_2026-06-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0ead42f0db52dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=20fc46279f198efe</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Talend, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95668eacef5ebd13</t>
+          <t>https://www.indeed.com/viewjob?jk=bec039b9620a5fef</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20fc46279f198efe</t>
+          <t>https://www.indeed.com/viewjob?jk=c48eb68de5366b63</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bec039b9620a5fef</t>
+          <t>https://www.indeed.com/viewjob?jk=212a79337c567fc4</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48eb68de5366b63</t>
+          <t>https://www.indeed.com/viewjob?jk=3048911b0454e84c</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212a79337c567fc4</t>
+          <t>https://www.indeed.com/viewjob?jk=02430a3484af15a3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3048911b0454e84c</t>
+          <t>https://www.indeed.com/viewjob?jk=a0ead42f0db52dd0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02430a3484af15a3</t>
+          <t>https://www.indeed.com/viewjob?jk=95668eacef5ebd13</t>
         </is>
       </c>
     </row>
@@ -3338,17 +3338,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JCTM</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1d90a9441d225d</t>
+          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>JCTM</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
+          <t>https://www.indeed.com/viewjob?jk=0f1d90a9441d225d</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073dcbe12166b408</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ba93b8542af918</t>
         </is>
       </c>
     </row>
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5283a1c7f91253d8</t>
+          <t>https://www.indeed.com/viewjob?jk=073dcbe12166b408</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Associate Actuary</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2413f123744bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5283a1c7f91253d8</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e40dedeb41804c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2413f123744bc5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data and AI Platform Engineer</t>
+          <t>Associate Actuary</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JELLYFISH</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Data Modeling, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
+          <t>https://www.indeed.com/viewjob?jk=45e40dedeb41804c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Intern - Full Stack Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Rad Cube LLC</t>
+          <t>Coverys</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceebe7f570acd23b</t>
+          <t>https://www.indeed.com/viewjob?jk=c259b85236c51107</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Coverys</t>
+          <t>JELLYFISH</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Data Modeling, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c259b85236c51107</t>
+          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Search Engineer</t>
+          <t>Intern - Full Stack Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Rad Cube LLC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b805c6c3ef2ef74</t>
+          <t>https://www.indeed.com/viewjob?jk=ceebe7f570acd23b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Search Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af72bf959cb85028</t>
+          <t>https://www.indeed.com/viewjob?jk=1b805c6c3ef2ef74</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdbca4cb9ae66f3</t>
+          <t>https://www.indeed.com/viewjob?jk=af72bf959cb85028</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2bbd584cafb766</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdbca4cb9ae66f3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f49ef023c8c96de</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2bbd584cafb766</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e7d8a3a432eba9</t>
+          <t>https://www.indeed.com/viewjob?jk=5f49ef023c8c96de</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf46770fd8ff6a55</t>
+          <t>https://www.indeed.com/viewjob?jk=68e7d8a3a432eba9</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Data &amp; AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>ZENO Group</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70e3e5b69eb2b62</t>
+          <t>https://www.indeed.com/viewjob?jk=bf46770fd8ff6a55</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Platform Engineer, Data &amp; AI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92021aa8ff2e1919</t>
+          <t>https://www.indeed.com/viewjob?jk=f70e3e5b69eb2b62</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e05275f5681930</t>
+          <t>https://www.indeed.com/viewjob?jk=92021aa8ff2e1919</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c6a7cf5bcefcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=74e05275f5681930</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e8a0f3adb10969c</t>
+          <t>https://www.indeed.com/viewjob?jk=17c6a7cf5bcefcd6</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr Automation Engineer Sales</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Raya Workforce</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d641f8b88bb4c</t>
+          <t>https://www.indeed.com/viewjob?jk=21e43ea584d339bf</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - US</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>GreenBox Capital</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0eba562e0eef18</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d641f8b88bb4c</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Backend Engineer - US</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GreenBox Capital</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,17 +4336,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796a5092268ae3dc</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0eba562e0eef18</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99dcfa53429fedf3</t>
+          <t>https://www.indeed.com/viewjob?jk=796a5092268ae3dc</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CADRE GOVERNMENT SOLUTIONS</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Kafka, Kafka Connect, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a874a7bc98d4c6bb</t>
+          <t>https://www.indeed.com/viewjob?jk=99dcfa53429fedf3</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr Automation Engineer Sales</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Raya Workforce</t>
+          <t>CADRE GOVERNMENT SOLUTIONS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Woodstock, VT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Scala, Kafka, Kafka Connect, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,19 +4451,19 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21e43ea584d339bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a874a7bc98d4c6bb</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PostgreSQL, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c582c80db561b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e8a0f3adb10969c</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2373638</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Scala, SQL Server, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Spark, PostgreSQL, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333af030098f9b44</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c582c80db561b</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Internally Deployed Products</t>
+          <t>Senior Software Engineer - 2373638</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ClickUp</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,15 +4546,50 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
+          <t>Azure, Synapse Analytics, Scala, SQL Server, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=333af030098f9b44</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Internally Deployed Products</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ClickUp</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
           <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, GCP, BigQuery, ETL, CI/CD</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7eb34b68319c8362</t>
         </is>

--- a/results/job_matches_2026-06-30.xlsx
+++ b/results/job_matches_2026-06-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,87 +748,87 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS SysOp Admin/DevOps Engineer</t>
+          <t>Sr. Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Neubus, Inc.</t>
+          <t>Diversify</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45e55bba1cdc0f9</t>
+          <t>https://www.indeed.com/viewjob?jk=61dfb2e97bef5956</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Integrations Engineer</t>
+          <t>Data and Insight Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Diversify</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Databricks, Hadoop, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61dfb2e97bef5956</t>
+          <t>https://www.indeed.com/viewjob?jk=cece0455bb6da18d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data and Insight Analyst</t>
+          <t>Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>The Data Sherpas</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,52 +836,52 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cece0455bb6da18d</t>
+          <t>https://www.indeed.com/viewjob?jk=212dc5034cb8bca8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - GCP</t>
+          <t>Senior Software Engineer- Big Data &amp; MCP, Data Foundations</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Data Sherpas</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, Scala, NoSQL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212dc5034cb8bca8</t>
+          <t>https://www.indeed.com/viewjob?jk=12e6bda7c4edc743</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e6bda7c4edc743</t>
+          <t>https://www.indeed.com/viewjob?jk=c603d89b037c27ac</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Big Data &amp; MCP, Data Foundations</t>
+          <t>Databricks Engineer and Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c603d89b037c27ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5f0ddbe29bf07cc0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks Engineer and Architect</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f0ddbe29bf07cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=b36e8e54920f0198</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36e8e54920f0198</t>
+          <t>https://www.indeed.com/viewjob?jk=03116dd5f77c4a08</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03116dd5f77c4a08</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca581db51f25003</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Senior IT Big Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca581db51f25003</t>
+          <t>https://www.indeed.com/viewjob?jk=805d9159d3aff63f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805d9159d3aff63f</t>
+          <t>https://www.indeed.com/viewjob?jk=8020391c43706e33</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer III - ATI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Willdan</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8020391c43706e33</t>
+          <t>https://www.indeed.com/viewjob?jk=8a9b04ee6e058585</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III - ATI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a9b04ee6e058585</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea10b210ba9e582</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, DevOps</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea10b210ba9e582</t>
+          <t>https://www.indeed.com/viewjob?jk=d3933dfeda45c057</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fullstack Developer_Tempe, AZ</t>
+          <t>AWS Software Engineer III-ETL/AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ccdf3f7c3217993</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2de7adcc27fce6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Engineer, DevOps</t>
+          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3933dfeda45c057</t>
+          <t>https://www.indeed.com/viewjob?jk=5c44ee92aa2c8400</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java &amp; AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Diversified Services Network, Inc.</t>
+          <t>Avaya</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
+          <t>Azure, Databricks, Hive, Spark, PySpark, Scala, ETL, ELT, Power BI, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=960399573e934589</t>
+          <t>https://www.indeed.com/viewjob?jk=626f550b7d7b1c09</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java &amp; AWS)</t>
+          <t>Software Engineer, Data (L1)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Diversified Services Network, Inc.</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, Azure, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51349eeea9315e96</t>
+          <t>https://www.indeed.com/viewjob?jk=de33f3f460768669</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AWS Software Engineer III-ETL/AI</t>
+          <t>Software Engineer, Data (L1)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2de7adcc27fce6</t>
+          <t>https://www.indeed.com/viewjob?jk=5a58fca26aa0b565</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c44ee92aa2c8400</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5f1d848e75885</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Avaya</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hive, Spark, PySpark, Scala, ETL, ELT, Power BI, GitHub Actions</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626f550b7d7b1c09</t>
+          <t>https://www.indeed.com/viewjob?jk=ea91a33e0a092959</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L1)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de33f3f460768669</t>
+          <t>https://www.indeed.com/viewjob?jk=a75cb5876ca6eeca</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L1)</t>
+          <t>ML Ops Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Circadia Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>AWS, S3, IAM, RDS, Spark, Dask, Snowflake, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a58fca26aa0b565</t>
+          <t>https://www.indeed.com/viewjob?jk=b91c752a8c427fd0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - Visual AI Technology</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5f1d848e75885</t>
+          <t>https://www.indeed.com/viewjob?jk=2bb194dac269cfc4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Forward Deployment Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>North Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea91a33e0a092959</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb2133b885b233e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
+          <t>Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala, Spark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75cb5876ca6eeca</t>
+          <t>https://www.indeed.com/viewjob?jk=65c09af802c5ffa3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Platform Architect</t>
+          <t>Data Engineer III, Development</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Clark Construction</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4607a264c3f31959</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f5ff112c1e4fbb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ML Ops Engineer</t>
+          <t>Associate Data Engineer / Data Engineer II / Senior Data Engineer (REMOTE)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Circadia Health</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Spark, Dask, Snowflake, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b91c752a8c427fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=665858153a76bc87</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III - Visual AI Technology</t>
+          <t>Databricks Platform &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,59 +1756,59 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bb194dac269cfc4</t>
+          <t>https://www.indeed.com/viewjob?jk=f4b537ec115b25d9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>NLM Cloud Engineer I</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>North Andover, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb2133b885b233e</t>
+          <t>https://www.indeed.com/viewjob?jk=f53c7c2bf6f1f5a7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Creve Coeur, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c09af802c5ffa3</t>
+          <t>https://www.indeed.com/viewjob?jk=3fed8aee2bab65bb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer/Architect - MS Fabric</t>
+          <t>Specialist - Software Development &amp; Engineering</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>EMR, RDS, Data Factory, Medallion Architecture, Dataflow, Hadoop, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baea501e7691a719</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4a561dc1cddafc</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer III, Development</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark, Kafka</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f5ff112c1e4fbb</t>
+          <t>https://www.indeed.com/viewjob?jk=baf9b523ed48e61a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Associate Data Engineer / Data Engineer II / Senior Data Engineer (REMOTE)</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=665858153a76bc87</t>
+          <t>https://www.indeed.com/viewjob?jk=5703940eacfe4257</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Databricks Platform &amp; Data Engineer</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4b537ec115b25d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3fdf8e05e3832326</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer I</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f53c7c2bf6f1f5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e28f7c9f9313edca</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Creve Coeur, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fed8aee2bab65bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1655be98963b6d30</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Specialist - Software Development &amp; Engineering</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4a561dc1cddafc</t>
+          <t>https://www.indeed.com/viewjob?jk=d57dce62ea127658</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fracht Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf9b523ed48e61a</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa96d3d36ceb7ae</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashua, NH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5703940eacfe4257</t>
+          <t>https://www.indeed.com/viewjob?jk=2490431387959f09</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashua, NH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fdf8e05e3832326</t>
+          <t>https://www.indeed.com/viewjob?jk=df0b13a3eb9c3062</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28f7c9f9313edca</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbc7c313d9e51ca</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Union City, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1655be98963b6d30</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d63ab0e4452de4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Blob Storage, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57dce62ea127658</t>
+          <t>https://www.indeed.com/viewjob?jk=ac49aa80fd785089</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Austin, TX - 2373630</t>
+          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, Data Modeling, Splunk</t>
+          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ecbcebb77acdc85</t>
+          <t>https://www.indeed.com/viewjob?jk=a0ead42f0db52dd0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ML Search Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fracht Group</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa96d3d36ceb7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=f3eed5895ede4859</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Azure, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2490431387959f09</t>
+          <t>https://www.indeed.com/viewjob?jk=3a31d611f67e9e2c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>MLOps Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df0b13a3eb9c3062</t>
+          <t>https://www.indeed.com/viewjob?jk=dae99e1ea457637a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
+          <t>ETL/Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>JCTM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Informatica PowerCenter, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbc7c313d9e51ca</t>
+          <t>https://www.indeed.com/viewjob?jk=84b5e94eddb1f9ba</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Intellivo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Union City, NJ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d63ab0e4452de4</t>
+          <t>https://www.indeed.com/viewjob?jk=03a247e4c9f8838e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Dir, Full Stack Data Scientist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac49aa80fd785089</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5df2a862bf9db8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20fc46279f198efe</t>
+          <t>https://www.indeed.com/viewjob?jk=92f5d55a58f8c38c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>New Boston, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bec039b9620a5fef</t>
+          <t>https://www.indeed.com/viewjob?jk=021284abbf4c58c0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Full Stack, Data &amp; Analytics Engineer (Agency Temp)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,102 +2631,102 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48eb68de5366b63</t>
+          <t>https://www.indeed.com/viewjob?jk=1ec69ba27334413b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Data Engineer - DevOps</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>ADG Tech Consulting</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212a79337c567fc4</t>
+          <t>https://www.indeed.com/viewjob?jk=e9b07407edcc90ef</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3048911b0454e84c</t>
+          <t>https://www.indeed.com/viewjob?jk=64cfca332d489410</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Solutions Architect II - Omnichannel</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02430a3484af15a3</t>
+          <t>https://www.indeed.com/viewjob?jk=51e91e41bcce9db6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>JCTM</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0ead42f0db52dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=0f1d90a9441d225d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Talend, dbt</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95668eacef5ebd13</t>
+          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ML Search Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,102 +2841,102 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3eed5895ede4859</t>
+          <t>https://www.indeed.com/viewjob?jk=f587f9ae6e2cdaae</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>IAM Operations Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Azure, CI/CD</t>
+          <t>AWS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a31d611f67e9e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=f1efb9ed7d3c48c5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer - 2373611</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Entiovi Technologies Private Limited</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bengal, IN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e4cfd29eb8d796</t>
+          <t>https://www.indeed.com/viewjob?jk=f89dc1b57a628321</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MLOps Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>NFI Industries</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dae99e1ea457637a</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9c3d571174ee0c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ETL/Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JCTM</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Informatica PowerCenter, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b5e94eddb1f9ba</t>
+          <t>https://www.indeed.com/viewjob?jk=602b89794c6d97b1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, PostgreSQL, MySQL, Cassandra, Splunk, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,172 +3016,172 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33da34be38b547b0</t>
+          <t>https://www.indeed.com/viewjob?jk=1a86f04695064d5c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Engineer (contract)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Intellivo</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a247e4c9f8838e</t>
+          <t>https://www.indeed.com/viewjob?jk=7bbb3ea9ee7ee707</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>INFORMATION SYSTEMS OFFICER, P3</t>
+          <t>Senior Systems Engineer (Ansible Automation Platform / Hybrid Cloud)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>United Nations</t>
+          <t>DAS Federal</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab00abb249e3052</t>
+          <t>https://www.indeed.com/viewjob?jk=c50a892c497ffe06</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Associate Dir, Full Stack Data Scientist</t>
+          <t>Senior Product Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>Ticket Takedown LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>BigQuery, Scala, NoSQL, Data Modeling, Docker, pytest, Airflow, Apache Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5df2a862bf9db8</t>
+          <t>https://www.indeed.com/viewjob?jk=55148fbc10cb871e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f5d55a58f8c38c</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ba93b8542af918</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>APLOMB Technologies</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New Boston, IL, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=021284abbf4c58c0</t>
+          <t>https://www.indeed.com/viewjob?jk=073dcbe12166b408</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer (Agency Temp)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ec69ba27334413b</t>
+          <t>https://www.indeed.com/viewjob?jk=5283a1c7f91253d8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Associate Actuary</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Trulieve</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2502fbaa4654c499</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2413f123744bc5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Associate Actuary</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f587f9ae6e2cdaae</t>
+          <t>https://www.indeed.com/viewjob?jk=45e40dedeb41804c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Solutions Architect II - Omnichannel</t>
+          <t>Senior Data and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>JELLYFISH</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Data Modeling, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,19 +3331,19 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51e91e41bcce9db6</t>
+          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Coverys</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3352,11 +3352,11 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
+          <t>https://www.indeed.com/viewjob?jk=c259b85236c51107</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Intern - Full Stack Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JCTM</t>
+          <t>Rad Cube LLC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1d90a9441d225d</t>
+          <t>https://www.indeed.com/viewjob?jk=ceebe7f570acd23b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Search Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Entiovi Technologies Private Limited</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bengal, IN, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89dc1b57a628321</t>
+          <t>https://www.indeed.com/viewjob?jk=1b805c6c3ef2ef74</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=602b89794c6d97b1</t>
+          <t>https://www.indeed.com/viewjob?jk=af72bf959cb85028</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a86f04695064d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdbca4cb9ae66f3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Database Engineer (contract)</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bbb3ea9ee7ee707</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2bbd584cafb766</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Ansible Automation Platform / Hybrid Cloud)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DAS Federal</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Docker</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,67 +3576,67 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50a892c497ffe06</t>
+          <t>https://www.indeed.com/viewjob?jk=5f49ef023c8c96de</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ba93b8542af918</t>
+          <t>https://www.indeed.com/viewjob?jk=68e7d8a3a432eba9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>ZENO Group</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,137 +3646,137 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073dcbe12166b408</t>
+          <t>https://www.indeed.com/viewjob?jk=bf46770fd8ff6a55</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5283a1c7f91253d8</t>
+          <t>https://www.indeed.com/viewjob?jk=92021aa8ff2e1919</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Associate Actuary</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2413f123744bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=74e05275f5681930</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Associate Actuary</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e40dedeb41804c</t>
+          <t>https://www.indeed.com/viewjob?jk=17c6a7cf5bcefcd6</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Platform Engineer, Data &amp; AI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Coverys</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,19 +3786,19 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c259b85236c51107</t>
+          <t>https://www.indeed.com/viewjob?jk=f70e3e5b69eb2b62</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data and AI Platform Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JELLYFISH</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3807,11 +3807,11 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Data Modeling, ELT, dbt, CI/CD</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,67 +3821,67 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d641f8b88bb4c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Intern - Full Stack Developer</t>
+          <t>Senior Backend Engineer - US</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Rad Cube LLC</t>
+          <t>GreenBox Capital</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceebe7f570acd23b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0eba562e0eef18</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Search Engineer</t>
+          <t>Sr Automation Engineer Sales</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Raya Workforce</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b805c6c3ef2ef74</t>
+          <t>https://www.indeed.com/viewjob?jk=21e43ea584d339bf</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af72bf959cb85028</t>
+          <t>https://www.indeed.com/viewjob?jk=796a5092268ae3dc</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdbca4cb9ae66f3</t>
+          <t>https://www.indeed.com/viewjob?jk=99dcfa53429fedf3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>CADRE GOVERNMENT SOLUTIONS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Scala, Kafka, Kafka Connect, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2bbd584cafb766</t>
+          <t>https://www.indeed.com/viewjob?jk=a874a7bc98d4c6bb</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f49ef023c8c96de</t>
+          <t>https://www.indeed.com/viewjob?jk=2e8a0f3adb10969c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PostgreSQL, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e7d8a3a432eba9</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c582c80db561b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - 2373638</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Azure, Synapse Analytics, Scala, SQL Server, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,497 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf46770fd8ff6a55</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer, Data &amp; AI</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>National Debt Relief</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f70e3e5b69eb2b62</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Data &amp; AI Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Revstar</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92021aa8ff2e1919</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Data &amp; AI Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Revstar</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74e05275f5681930</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Data &amp; AI Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Revstar</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=17c6a7cf5bcefcd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Sr Automation Engineer Sales</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Raya Workforce</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Woodstock, VT, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21e43ea584d339bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Empirx Health</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d641f8b88bb4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer - US</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>GreenBox Capital</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0eba562e0eef18</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=796a5092268ae3dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Bridgewater, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99dcfa53429fedf3</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Kafka Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>CADRE GOVERNMENT SOLUTIONS</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Scala, Kafka, Kafka Connect, ETL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a874a7bc98d4c6bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Machine Learning Intern</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Aivra Health</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e8a0f3adb10969c</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Magnet Forensics</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PostgreSQL, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c582c80db561b</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - 2373638</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Azure, Synapse Analytics, Scala, SQL Server, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=333af030098f9b44</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Internally Deployed Products</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>ClickUp</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, GCP, BigQuery, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb34b68319c8362</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-30.xlsx
+++ b/results/job_matches_2026-06-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Green Mountain Power</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Colchester, VT, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.7</v>
+        <v>24.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Google Cloud Platform, GCP, Hadoop, HDFS, Hive</t>
+          <t>AWS, EMR, Lambda, Kinesis, S3, SQS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d9f58a4baa94d06</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4c425e913ad44b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Architect</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.3</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, S3, SQS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4c425e913ad44b</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb2fa0a1c1af3df</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb2fa0a1c1af3df</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8650d270076806</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8650d270076806</t>
+          <t>https://www.indeed.com/viewjob?jk=577e95a781bd4589</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Lake Saint Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,42 +636,42 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577e95a781bd4589</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2775012dc3e1f4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lake Saint Louis, MO, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2775012dc3e1f4</t>
+          <t>https://www.indeed.com/viewjob?jk=c9fc4b01a8878948</t>
         </is>
       </c>
     </row>
@@ -706,94 +706,94 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9fc4b01a8878948</t>
+          <t>https://www.indeed.com/viewjob?jk=de1fca8ed87b85de</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Diversify</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1fca8ed87b85de</t>
+          <t>https://www.indeed.com/viewjob?jk=61dfb2e97bef5956</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Integrations Engineer</t>
+          <t>Data and Insight Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Diversify</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Databricks, Hadoop, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61dfb2e97bef5956</t>
+          <t>https://www.indeed.com/viewjob?jk=cece0455bb6da18d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data and Insight Analyst</t>
+          <t>Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>The Data Sherpas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,52 +801,52 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cece0455bb6da18d</t>
+          <t>https://www.indeed.com/viewjob?jk=212dc5034cb8bca8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - GCP</t>
+          <t>Senior Software Engineer- Big Data &amp; MCP, Data Foundations</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Data Sherpas</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, Scala, NoSQL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212dc5034cb8bca8</t>
+          <t>https://www.indeed.com/viewjob?jk=12e6bda7c4edc743</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e6bda7c4edc743</t>
+          <t>https://www.indeed.com/viewjob?jk=c603d89b037c27ac</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Big Data &amp; MCP, Data Foundations</t>
+          <t>Databricks Engineer and Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Lincoln Financial</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c603d89b037c27ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5f0ddbe29bf07cc0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Databricks Engineer and Architect</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f0ddbe29bf07cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=b36e8e54920f0198</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36e8e54920f0198</t>
+          <t>https://www.indeed.com/viewjob?jk=03116dd5f77c4a08</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03116dd5f77c4a08</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca581db51f25003</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Senior IT Big Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca581db51f25003</t>
+          <t>https://www.indeed.com/viewjob?jk=805d9159d3aff63f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805d9159d3aff63f</t>
+          <t>https://www.indeed.com/viewjob?jk=8020391c43706e33</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer III - ATI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Willdan</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8020391c43706e33</t>
+          <t>https://www.indeed.com/viewjob?jk=8a9b04ee6e058585</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III - ATI</t>
+          <t>Senior Engineer, DevOps</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a9b04ee6e058585</t>
+          <t>https://www.indeed.com/viewjob?jk=d3933dfeda45c057</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Software Engineer III-ETL/AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea10b210ba9e582</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2de7adcc27fce6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Engineer, DevOps</t>
+          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3933dfeda45c057</t>
+          <t>https://www.indeed.com/viewjob?jk=5c44ee92aa2c8400</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS Software Engineer III-ETL/AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Avaya</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>Azure, Databricks, Hive, Spark, PySpark, Scala, ETL, ELT, Power BI, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2de7adcc27fce6</t>
+          <t>https://www.indeed.com/viewjob?jk=626f550b7d7b1c09</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
+          <t>Software Engineer, Data (L1)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c44ee92aa2c8400</t>
+          <t>https://www.indeed.com/viewjob?jk=de33f3f460768669</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Data (L1)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Avaya</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hive, Spark, PySpark, Scala, ETL, ELT, Power BI, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626f550b7d7b1c09</t>
+          <t>https://www.indeed.com/viewjob?jk=5a58fca26aa0b565</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L1)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de33f3f460768669</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5f1d848e75885</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L1)</t>
+          <t>AI Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a58fca26aa0b565</t>
+          <t>https://www.indeed.com/viewjob?jk=ea91a33e0a092959</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5f1d848e75885</t>
+          <t>https://www.indeed.com/viewjob?jk=a75cb5876ca6eeca</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Forward Deployment Engineer</t>
+          <t>ML Ops Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Circadia Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, S3, IAM, RDS, Spark, Dask, Snowflake, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea91a33e0a092959</t>
+          <t>https://www.indeed.com/viewjob?jk=b91c752a8c427fd0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Software Engineer III - Visual AI Technology</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75cb5876ca6eeca</t>
+          <t>https://www.indeed.com/viewjob?jk=2bb194dac269cfc4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ML Ops Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Circadia Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>North Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Spark, Dask, Snowflake, MLOps, MLflow, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b91c752a8c427fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb2133b885b233e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer III - Visual AI Technology</t>
+          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD</t>
+          <t>Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala, Spark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bb194dac269cfc4</t>
+          <t>https://www.indeed.com/viewjob?jk=65c09af802c5ffa3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer III, Development</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>North Andover, MA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb2133b885b233e</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f5ff112c1e4fbb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
+          <t>Associate Data Engineer / Data Engineer II / Senior Data Engineer (REMOTE)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c09af802c5ffa3</t>
+          <t>https://www.indeed.com/viewjob?jk=665858153a76bc87</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer III, Development</t>
+          <t>Databricks Platform &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f5ff112c1e4fbb</t>
+          <t>https://www.indeed.com/viewjob?jk=f4b537ec115b25d9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Associate Data Engineer / Data Engineer II / Senior Data Engineer (REMOTE)</t>
+          <t>NLM Cloud Engineer I</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=665858153a76bc87</t>
+          <t>https://www.indeed.com/viewjob?jk=f53c7c2bf6f1f5a7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Databricks Platform &amp; Data Engineer</t>
+          <t>AWS Databricks Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Solvstaff</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4b537ec115b25d9</t>
+          <t>https://www.indeed.com/viewjob?jk=5a9a04b047de59e9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer I</t>
+          <t>Senior Backend Engineer, Core APIs</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Fingerprint</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f53c7c2bf6f1f5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=89f151cbc6d5b613</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Specialist - Software Development &amp; Engineering</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Creve Coeur, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fed8aee2bab65bb</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4a561dc1cddafc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Specialist - Software Development &amp; Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4a561dc1cddafc</t>
+          <t>https://www.indeed.com/viewjob?jk=baf9b523ed48e61a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Creve Coeur, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf9b523ed48e61a</t>
+          <t>https://www.indeed.com/viewjob?jk=3fed8aee2bab65bb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>Fracht Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5703940eacfe4257</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa96d3d36ceb7ae</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashua, NH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fdf8e05e3832326</t>
+          <t>https://www.indeed.com/viewjob?jk=2490431387959f09</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Nashua, NH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28f7c9f9313edca</t>
+          <t>https://www.indeed.com/viewjob?jk=df0b13a3eb9c3062</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1655be98963b6d30</t>
+          <t>https://www.indeed.com/viewjob?jk=2048b8f9fc33e871</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer - DevTools</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Blob Storage, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57dce62ea127658</t>
+          <t>https://www.indeed.com/viewjob?jk=ac49aa80fd785089</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fracht Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Union City, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa96d3d36ceb7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d63ab0e4452de4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML Search Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2490431387959f09</t>
+          <t>https://www.indeed.com/viewjob?jk=f3eed5895ede4859</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Azure, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df0b13a3eb9c3062</t>
+          <t>https://www.indeed.com/viewjob?jk=3a31d611f67e9e2c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
+          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
+          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbc7c313d9e51ca</t>
+          <t>https://www.indeed.com/viewjob?jk=a0ead42f0db52dd0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MLOps Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Union City, NJ, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d63ab0e4452de4</t>
+          <t>https://www.indeed.com/viewjob?jk=dae99e1ea457637a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ETL/Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>JCTM</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Informatica PowerCenter, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,129 +2281,129 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac49aa80fd785089</t>
+          <t>https://www.indeed.com/viewjob?jk=84b5e94eddb1f9ba</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Intellivo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0ead42f0db52dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=03a247e4c9f8838e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ML Search Engineer</t>
+          <t>DevOps Software Engineer Specialists</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, S3, RDS, Oracle, PostgreSQL, DynamoDB, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3eed5895ede4859</t>
+          <t>https://www.indeed.com/viewjob?jk=06e65c0f51719bda</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>6sense</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Azure, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a31d611f67e9e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=05703cc8519b448f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MLOps Engineer II</t>
+          <t>Associate Dir, Full Stack Data Scientist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dae99e1ea457637a</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5df2a862bf9db8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ETL/Data Engineer</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JCTM</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Informatica PowerCenter, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b5e94eddb1f9ba</t>
+          <t>https://www.indeed.com/viewjob?jk=92f5d55a58f8c38c</t>
         </is>
       </c>
     </row>
@@ -2468,82 +2468,82 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Intellivo</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>New Boston, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a247e4c9f8838e</t>
+          <t>https://www.indeed.com/viewjob?jk=021284abbf4c58c0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Associate Dir, Full Stack Data Scientist</t>
+          <t>Senior Data Engineer - DevOps</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>ADG Tech Consulting</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5df2a862bf9db8</t>
+          <t>https://www.indeed.com/viewjob?jk=e9b07407edcc90ef</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f5d55a58f8c38c</t>
+          <t>https://www.indeed.com/viewjob?jk=64cfca332d489410</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>APLOMB Technologies</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New Boston, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=021284abbf4c58c0</t>
+          <t>https://www.indeed.com/viewjob?jk=f587f9ae6e2cdaae</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer (Agency Temp)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>JCTM</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ec69ba27334413b</t>
+          <t>https://www.indeed.com/viewjob?jk=0f1d90a9441d225d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - DevOps</t>
+          <t>Solutions Architect II - Omnichannel</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ADG Tech Consulting</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9b07407edcc90ef</t>
+          <t>https://www.indeed.com/viewjob?jk=51e91e41bcce9db6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cfca332d489410</t>
+          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Solutions Architect II - Omnichannel</t>
+          <t>IAM Operations Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51e91e41bcce9db6</t>
+          <t>https://www.indeed.com/viewjob?jk=f1efb9ed7d3c48c5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JCTM</t>
+          <t>NFI Industries</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1d90a9441d225d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9c3d571174ee0c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
+          <t>https://www.indeed.com/viewjob?jk=602b89794c6d97b1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,94 +2841,94 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f587f9ae6e2cdaae</t>
+          <t>https://www.indeed.com/viewjob?jk=1a86f04695064d5c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IAM Operations Engineer</t>
+          <t>Database Engineer (contract)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1efb9ed7d3c48c5</t>
+          <t>https://www.indeed.com/viewjob?jk=7bbb3ea9ee7ee707</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Systems Engineer (Ansible Automation Platform / Hybrid Cloud)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Entiovi Technologies Private Limited</t>
+          <t>DAS Federal</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bengal, IN, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89dc1b57a628321</t>
+          <t>https://www.indeed.com/viewjob?jk=c50a892c497ffe06</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Product Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>Ticket Takedown LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>BigQuery, Scala, NoSQL, Data Modeling, Docker, pytest, Airflow, Apache Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9c3d571174ee0c</t>
+          <t>https://www.indeed.com/viewjob?jk=55148fbc10cb871e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=602b89794c6d97b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ba93b8542af918</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Search Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a86f04695064d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=1b805c6c3ef2ef74</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Database Engineer (contract)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bbb3ea9ee7ee707</t>
+          <t>https://www.indeed.com/viewjob?jk=073dcbe12166b408</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Ansible Automation Platform / Hybrid Cloud)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DAS Federal</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50a892c497ffe06</t>
+          <t>https://www.indeed.com/viewjob?jk=5283a1c7f91253d8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Product Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ticket Takedown LLC</t>
+          <t>Coverys</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>BigQuery, Scala, NoSQL, Data Modeling, Docker, pytest, Airflow, Apache Airflow, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55148fbc10cb871e</t>
+          <t>https://www.indeed.com/viewjob?jk=c259b85236c51107</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Associate Actuary</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ba93b8542af918</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2413f123744bc5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Actuary</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073dcbe12166b408</t>
+          <t>https://www.indeed.com/viewjob?jk=45e40dedeb41804c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Intern - Full Stack Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Rad Cube LLC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5283a1c7f91253d8</t>
+          <t>https://www.indeed.com/viewjob?jk=ceebe7f570acd23b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Associate Actuary</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,19 +3261,19 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2413f123744bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdbca4cb9ae66f3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Associate Actuary</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3282,11 +3282,11 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e40dedeb41804c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2bbd584cafb766</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data and AI Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JELLYFISH</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse, Data Modeling, ELT, dbt, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,129 +3331,129 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f49ef023c8c96de</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Coverys</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c259b85236c51107</t>
+          <t>https://www.indeed.com/viewjob?jk=92021aa8ff2e1919</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Intern - Full Stack Developer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Rad Cube LLC</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceebe7f570acd23b</t>
+          <t>https://www.indeed.com/viewjob?jk=74e05275f5681930</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Search Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b805c6c3ef2ef74</t>
+          <t>https://www.indeed.com/viewjob?jk=17c6a7cf5bcefcd6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af72bf959cb85028</t>
+          <t>https://www.indeed.com/viewjob?jk=2e8a0f3adb10969c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Git</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdbca4cb9ae66f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d641f8b88bb4c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, PostgreSQL, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2bbd584cafb766</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c582c80db561b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Backend Engineer - US</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GreenBox Capital</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f49ef023c8c96de</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0eba562e0eef18</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Senior Platform Engineer, Data &amp; AI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e7d8a3a432eba9</t>
+          <t>https://www.indeed.com/viewjob?jk=f70e3e5b69eb2b62</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Automation Engineer Sales</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>Raya Workforce</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf46770fd8ff6a55</t>
+          <t>https://www.indeed.com/viewjob?jk=21e43ea584d339bf</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92021aa8ff2e1919</t>
+          <t>https://www.indeed.com/viewjob?jk=796a5092268ae3dc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e05275f5681930</t>
+          <t>https://www.indeed.com/viewjob?jk=99dcfa53429fedf3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>CADRE GOVERNMENT SOLUTIONS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,367 +3741,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+          <t>AWS, API Gateway, RDS, Scala, Kafka, Kafka Connect, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c6a7cf5bcefcd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer, Data &amp; AI</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>National Debt Relief</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f70e3e5b69eb2b62</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Empirx Health</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d641f8b88bb4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer - US</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>GreenBox Capital</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0eba562e0eef18</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Sr Automation Engineer Sales</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Raya Workforce</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Woodstock, VT, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21e43ea584d339bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=796a5092268ae3dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Bridgewater, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99dcfa53429fedf3</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Kafka Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>CADRE GOVERNMENT SOLUTIONS</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Scala, Kafka, Kafka Connect, ETL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=a874a7bc98d4c6bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Machine Learning Intern</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Aivra Health</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e8a0f3adb10969c</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Magnet Forensics</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PostgreSQL, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c582c80db561b</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - 2373638</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Azure, Synapse Analytics, Scala, SQL Server, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=333af030098f9b44</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-30.xlsx
+++ b/results/job_matches_2026-06-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,105 +468,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Cloud Architect</t>
+          <t>Data Engineer - CSS, AIP and HPX Analytics</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.3</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, S3, SQS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Hadoop, Hive</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4c425e913ad44b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a78dd582651cf84</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Meridian Systematics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Azure, Hadoop, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb2fa0a1c1af3df</t>
+          <t>https://www.indeed.com/viewjob?jk=86f4cd04f1d7226b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
+          <t>Data Engineer - Temporary Worker</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Merkle, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8650d270076806</t>
+          <t>https://www.indeed.com/viewjob?jk=fd3608ce8fafa5b9</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577e95a781bd4589</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb2fa0a1c1af3df</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lake Saint Louis, MO, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,207 +636,207 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2775012dc3e1f4</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8650d270076806</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9fc4b01a8878948</t>
+          <t>https://www.indeed.com/viewjob?jk=577e95a781bd4589</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Lake Saint Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1fca8ed87b85de</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2775012dc3e1f4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Integrations Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diversify</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61dfb2e97bef5956</t>
+          <t>https://www.indeed.com/viewjob?jk=c9fc4b01a8878948</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data and Insight Analyst</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cece0455bb6da18d</t>
+          <t>https://www.indeed.com/viewjob?jk=de1fca8ed87b85de</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer - GCP</t>
+          <t>Sr. Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Data Sherpas</t>
+          <t>Diversify</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, Scala, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212dc5034cb8bca8</t>
+          <t>https://www.indeed.com/viewjob?jk=61dfb2e97bef5956</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Big Data &amp; MCP, Data Foundations</t>
+          <t>Data and Insight Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Databricks, Hadoop, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e6bda7c4edc743</t>
+          <t>https://www.indeed.com/viewjob?jk=cece0455bb6da18d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Big Data &amp; MCP, Data Foundations</t>
+          <t>Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>The Data Sherpas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c603d89b037c27ac</t>
+          <t>https://www.indeed.com/viewjob?jk=212dc5034cb8bca8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Databricks Engineer and Architect</t>
+          <t>Senior Software Engineer- Big Data &amp; MCP, Data Foundations</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lincoln Financial</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f0ddbe29bf07cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=12e6bda7c4edc743</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Senior Software Engineer- Big Data &amp; MCP, Data Foundations</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36e8e54920f0198</t>
+          <t>https://www.indeed.com/viewjob?jk=c603d89b037c27ac</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Databricks Engineer and Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Lincoln Financial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03116dd5f77c4a08</t>
+          <t>https://www.indeed.com/viewjob?jk=5f0ddbe29bf07cc0</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca581db51f25003</t>
+          <t>https://www.indeed.com/viewjob?jk=b36e8e54920f0198</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Engineer</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805d9159d3aff63f</t>
+          <t>https://www.indeed.com/viewjob?jk=03116dd5f77c4a08</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Willdan</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8020391c43706e33</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca581db51f25003</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III - ATI</t>
+          <t>Senior IT Big Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a9b04ee6e058585</t>
+          <t>https://www.indeed.com/viewjob?jk=805d9159d3aff63f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Engineer, DevOps</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3933dfeda45c057</t>
+          <t>https://www.indeed.com/viewjob?jk=8020391c43706e33</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Software Engineer III-ETL/AI</t>
+          <t>Software Engineer III - ATI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2de7adcc27fce6</t>
+          <t>https://www.indeed.com/viewjob?jk=8a9b04ee6e058585</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
+          <t>AWS Software Engineer III-ETL/AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c44ee92aa2c8400</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2de7adcc27fce6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Avaya</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hive, Spark, PySpark, Scala, ETL, ELT, Power BI, GitHub Actions</t>
+          <t>AWS, Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626f550b7d7b1c09</t>
+          <t>https://www.indeed.com/viewjob?jk=5c44ee92aa2c8400</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIs</t>
+          <t>Senior Full-Stack Software Engineer – Back-End Focused</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fingerprint</t>
+          <t>STAND TOGETHER</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89f151cbc6d5b613</t>
+          <t>https://www.indeed.com/viewjob?jk=27c394a83edfce01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Specialist - Software Development &amp; Engineering</t>
+          <t>Senior Backend Engineer, Core APIs</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Fingerprint</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,77 +1816,77 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4a561dc1cddafc</t>
+          <t>https://www.indeed.com/viewjob?jk=89f151cbc6d5b613</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Western Alliance Bank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf9b523ed48e61a</t>
+          <t>https://www.indeed.com/viewjob?jk=34c193d803b2a019</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Fracht Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Creve Coeur, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fed8aee2bab65bb</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa96d3d36ceb7ae</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fracht Group</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashua, NH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa96d3d36ceb7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2490431387959f09</t>
         </is>
       </c>
     </row>
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2490431387959f09</t>
+          <t>https://www.indeed.com/viewjob?jk=df0b13a3eb9c3062</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df0b13a3eb9c3062</t>
+          <t>https://www.indeed.com/viewjob?jk=2048b8f9fc33e871</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer II (US)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, Databricks, Blob Storage, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2048b8f9fc33e871</t>
+          <t>https://www.indeed.com/viewjob?jk=ac49aa80fd785089</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Union City, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac49aa80fd785089</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d63ab0e4452de4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Union City, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d63ab0e4452de4</t>
+          <t>https://www.indeed.com/viewjob?jk=a0ead42f0db52dd0</t>
         </is>
       </c>
     </row>
@@ -2148,25 +2148,25 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MLOps Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Azure, CI/CD</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,59 +2176,59 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a31d611f67e9e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=dae99e1ea457637a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Intellivo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0ead42f0db52dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=03a247e4c9f8838e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MLOps Engineer II</t>
+          <t>Gen AI Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>QualityAI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dae99e1ea457637a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6f26d72223ee99</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ETL/Data Engineer</t>
+          <t>DevOps Software Engineer Specialists</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JCTM</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Informatica PowerCenter, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Oracle, PostgreSQL, DynamoDB, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b5e94eddb1f9ba</t>
+          <t>https://www.indeed.com/viewjob?jk=06e65c0f51719bda</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Intellivo</t>
+          <t>6sense</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a247e4c9f8838e</t>
+          <t>https://www.indeed.com/viewjob?jk=05703cc8519b448f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer Specialists</t>
+          <t>Associate Dir, Full Stack Data Scientist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,104 +2341,104 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Oracle, PostgreSQL, DynamoDB, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e65c0f51719bda</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5df2a862bf9db8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6sense</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05703cc8519b448f</t>
+          <t>https://www.indeed.com/viewjob?jk=92f5d55a58f8c38c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Dir, Full Stack Data Scientist</t>
+          <t>Senior Data Engineer - DevOps</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>ADG Tech Consulting</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5df2a862bf9db8</t>
+          <t>https://www.indeed.com/viewjob?jk=e9b07407edcc90ef</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f5d55a58f8c38c</t>
+          <t>https://www.indeed.com/viewjob?jk=64cfca332d489410</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Software Development Test QE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>APLOMB Technologies</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New Boston, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,29 +2481,29 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, RDS, Spark, PySpark, SQL Server, MySQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=021284abbf4c58c0</t>
+          <t>https://www.indeed.com/viewjob?jk=56447c16c3ba977a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - DevOps</t>
+          <t>Senior Full Stack Software Engineer - CostCheck</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ADG Tech Consulting</t>
+          <t>BlueSight</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Athena, S3, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9b07407edcc90ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b724f0ef5f1675</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,112 +2551,112 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cfca332d489410</t>
+          <t>https://www.indeed.com/viewjob?jk=f587f9ae6e2cdaae</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f587f9ae6e2cdaae</t>
+          <t>https://www.indeed.com/viewjob?jk=46176023248faed5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JCTM</t>
+          <t>MediaRadar</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, SQL Server, ETL, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1d90a9441d225d</t>
+          <t>https://www.indeed.com/viewjob?jk=180b2fb1ba9c363d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Solutions Architect II - Omnichannel</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>NFI Industries</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51e91e41bcce9db6</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9c3d571174ee0c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,59 +2701,59 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
+          <t>https://www.indeed.com/viewjob?jk=602b89794c6d97b1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IAM Operations Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1efb9ed7d3c48c5</t>
+          <t>https://www.indeed.com/viewjob?jk=1a86f04695064d5c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer 2026 - US</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9c3d571174ee0c</t>
+          <t>https://www.indeed.com/viewjob?jk=13884b1c57640398</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=602b89794c6d97b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ba93b8542af918</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a86f04695064d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=073dcbe12166b408</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Database Engineer (contract)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bbb3ea9ee7ee707</t>
+          <t>https://www.indeed.com/viewjob?jk=5283a1c7f91253d8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Ansible Automation Platform / Hybrid Cloud)</t>
+          <t>Search Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DAS Federal</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50a892c497ffe06</t>
+          <t>https://www.indeed.com/viewjob?jk=1b805c6c3ef2ef74</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Product Engineer</t>
+          <t>IOS Developer + Node.js</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ticket Takedown LLC</t>
+          <t>SIGNITIVES</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>BigQuery, Scala, NoSQL, Data Modeling, Docker, pytest, Airflow, Apache Airflow, Git, Python</t>
+          <t>EMR, RDS, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55148fbc10cb871e</t>
+          <t>https://www.indeed.com/viewjob?jk=5fe2db57addb7567</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Senior Product Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>Ticket Takedown LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>BigQuery, Scala, NoSQL, Data Modeling, Docker, pytest, Airflow, Apache Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ba93b8542af918</t>
+          <t>https://www.indeed.com/viewjob?jk=55148fbc10cb871e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Search Engineer</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b805c6c3ef2ef74</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdbca4cb9ae66f3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073dcbe12166b408</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2bbd584cafb766</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5283a1c7f91253d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5f49ef023c8c96de</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>DevOps Engineer - International Project</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Coverys</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c259b85236c51107</t>
+          <t>https://www.indeed.com/viewjob?jk=e71d6f8a3530ffa9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate Actuary</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2413f123744bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c51ea63d2c9240e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Associate Actuary</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Wildfire Defense Systems</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,59 +3191,59 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e40dedeb41804c</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d641f8b88bb4c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Intern - Full Stack Developer</t>
+          <t>Senior Backend Engineer - US</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Rad Cube LLC</t>
+          <t>GreenBox Capital</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceebe7f570acd23b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0eba562e0eef18</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Senior Platform Engineer, Data &amp; AI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Git</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdbca4cb9ae66f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f70e3e5b69eb2b62</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Sr Automation Engineer Sales</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>Raya Workforce</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2bbd584cafb766</t>
+          <t>https://www.indeed.com/viewjob?jk=21e43ea584d339bf</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f49ef023c8c96de</t>
+          <t>https://www.indeed.com/viewjob?jk=2e8a0f3adb10969c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+          <t>AWS, RDS, Azure, Spark, PostgreSQL, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92021aa8ff2e1919</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c582c80db561b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e05275f5681930</t>
+          <t>https://www.indeed.com/viewjob?jk=796a5092268ae3dc</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,332 +3426,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c6a7cf5bcefcd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Machine Learning Intern</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Aivra Health</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e8a0f3adb10969c</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Empirx Health</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d641f8b88bb4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Magnet Forensics</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PostgreSQL, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c582c80db561b</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer - US</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>GreenBox Capital</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0eba562e0eef18</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer, Data &amp; AI</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>National Debt Relief</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f70e3e5b69eb2b62</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Sr Automation Engineer Sales</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Raya Workforce</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Woodstock, VT, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21e43ea584d339bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=796a5092268ae3dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Bridgewater, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=99dcfa53429fedf3</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Kafka Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>CADRE GOVERNMENT SOLUTIONS</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Scala, Kafka, Kafka Connect, ETL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a874a7bc98d4c6bb</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-30.xlsx
+++ b/results/job_matches_2026-06-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer - Temporary Worker</t>
+          <t>Senior Development Ops Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Merkle, Inc.</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, HDFS, HBase, Spark, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,77 +566,77 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd3608ce8fafa5b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b43701e8a621c350</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
+          <t>Data Engineer - Temporary Worker</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Dentsu</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb2fa0a1c1af3df</t>
+          <t>https://www.indeed.com/viewjob?jk=f79b9ae386c30e15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
+          <t>Data Engineer - Temporary Worker</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Merkle, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8650d270076806</t>
+          <t>https://www.indeed.com/viewjob?jk=fd3608ce8fafa5b9</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577e95a781bd4589</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb2fa0a1c1af3df</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lake Saint Louis, MO, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,164 +706,164 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2775012dc3e1f4</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8650d270076806</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9fc4b01a8878948</t>
+          <t>https://www.indeed.com/viewjob?jk=577e95a781bd4589</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Lake Saint Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1fca8ed87b85de</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2775012dc3e1f4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Integrations Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Diversify</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61dfb2e97bef5956</t>
+          <t>https://www.indeed.com/viewjob?jk=c9fc4b01a8878948</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data and Insight Analyst</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cece0455bb6da18d</t>
+          <t>https://www.indeed.com/viewjob?jk=de1fca8ed87b85de</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - GCP</t>
+          <t>Data and Insight Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Data Sherpas</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, Scala, NoSQL</t>
+          <t>RDS, Databricks, Hadoop, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212dc5034cb8bca8</t>
+          <t>https://www.indeed.com/viewjob?jk=cece0455bb6da18d</t>
         </is>
       </c>
     </row>
@@ -958,60 +958,60 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks Engineer and Architect</t>
+          <t>Senior IT Big Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lincoln Financial</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f0ddbe29bf07cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=805d9159d3aff63f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,102 +1021,102 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36e8e54920f0198</t>
+          <t>https://www.indeed.com/viewjob?jk=8020391c43706e33</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Software Engineer, Data (L1)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03116dd5f77c4a08</t>
+          <t>https://www.indeed.com/viewjob?jk=de33f3f460768669</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Software Engineer, Data (L1)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca581db51f25003</t>
+          <t>https://www.indeed.com/viewjob?jk=5a58fca26aa0b565</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805d9159d3aff63f</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5f1d848e75885</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>ML Ops Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Willdan</t>
+          <t>Circadia Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Spark, Dask, Snowflake, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8020391c43706e33</t>
+          <t>https://www.indeed.com/viewjob?jk=b91c752a8c427fd0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III - ATI</t>
+          <t>Software Engineer III - Visual AI Technology</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a9b04ee6e058585</t>
+          <t>https://www.indeed.com/viewjob?jk=2bb194dac269cfc4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Software Engineer III-ETL/AI</t>
+          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala, Spark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2de7adcc27fce6</t>
+          <t>https://www.indeed.com/viewjob?jk=65c09af802c5ffa3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
+          <t>Data Engineer III, Development</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,242 +1266,242 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c44ee92aa2c8400</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f5ff112c1e4fbb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L1)</t>
+          <t>Associate Data Engineer / Data Engineer II / Senior Data Engineer (REMOTE)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de33f3f460768669</t>
+          <t>https://www.indeed.com/viewjob?jk=665858153a76bc87</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L1)</t>
+          <t>Databricks Platform &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a58fca26aa0b565</t>
+          <t>https://www.indeed.com/viewjob?jk=f4b537ec115b25d9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Databricks Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>Solvstaff</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5f1d848e75885</t>
+          <t>https://www.indeed.com/viewjob?jk=5a9a04b047de59e9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Forward Deployment Engineer</t>
+          <t>Senior Full-Stack Software Engineer – Back-End Focused</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>STAND TOGETHER</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea91a33e0a092959</t>
+          <t>https://www.indeed.com/viewjob?jk=27c394a83edfce01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Backend Engineer, Core APIs</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fingerprint</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75cb5876ca6eeca</t>
+          <t>https://www.indeed.com/viewjob?jk=89f151cbc6d5b613</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ML Ops Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Circadia Health</t>
+          <t>Western Alliance Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Spark, Dask, Snowflake, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b91c752a8c427fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=34c193d803b2a019</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III - Visual AI Technology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Fracht Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,172 +1511,172 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bb194dac269cfc4</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa96d3d36ceb7ae</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect (P4642)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>North Andover, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb2133b885b233e</t>
+          <t>https://www.indeed.com/viewjob?jk=1660a4cf0a8045d0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
+          <t>Data Architect (P4642)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lambda, Azure, Data Factory, Hadoop, HDFS, Hive, MapReduce, Flume, Impala, Spark</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c09af802c5ffa3</t>
+          <t>https://www.indeed.com/viewjob?jk=39b5a4b6b25e561f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer III, Development</t>
+          <t>Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f5ff112c1e4fbb</t>
+          <t>https://www.indeed.com/viewjob?jk=2048b8f9fc33e871</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Associate Data Engineer / Data Engineer II / Senior Data Engineer (REMOTE)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=665858153a76bc87</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0c72a3fb65e08</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Databricks Platform &amp; Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, Blob Storage, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,102 +1686,102 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4b537ec115b25d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ac49aa80fd785089</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Union City, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f53c7c2bf6f1f5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d63ab0e4452de4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AWS Databricks Architect</t>
+          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Solvstaff</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a9a04b047de59e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a0ead42f0db52dd0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer – Back-End Focused</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>STAND TOGETHER</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c394a83edfce01</t>
+          <t>https://www.indeed.com/viewjob?jk=675596684c392e8e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIs</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fingerprint</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, Glue, S3, RDS, Databricks, Unity Catalog, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,172 +1826,172 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89f151cbc6d5b613</t>
+          <t>https://www.indeed.com/viewjob?jk=e4db27c4a07cdc78</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Western Alliance Bank</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, Snowflake, ETL, Power BI</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c193d803b2a019</t>
+          <t>https://www.indeed.com/viewjob?jk=dae99e1ea457637a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Gen AI Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fracht Group</t>
+          <t>QualityAI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa96d3d36ceb7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6f26d72223ee99</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Software Engineer Specialists</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, RDS, Oracle, PostgreSQL, DynamoDB, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2490431387959f09</t>
+          <t>https://www.indeed.com/viewjob?jk=06e65c0f51719bda</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>6sense</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df0b13a3eb9c3062</t>
+          <t>https://www.indeed.com/viewjob?jk=05703cc8519b448f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer II (US)</t>
+          <t>Expert Analyst Data Management (Epic ODBA Cert Req'd)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2048b8f9fc33e871</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4bf16bfeb52f1c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Dir, Full Stack Data Scientist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac49aa80fd785089</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5df2a862bf9db8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer - AI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>LogicMonitor</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Union City, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Spark, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,207 +2071,207 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d63ab0e4452de4</t>
+          <t>https://www.indeed.com/viewjob?jk=951fb41e37160d69</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
+          <t>Senior Data Engineer - DevOps</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>ADG Tech Consulting</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0ead42f0db52dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=e9b07407edcc90ef</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ML Search Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3eed5895ede4859</t>
+          <t>https://www.indeed.com/viewjob?jk=64cfca332d489410</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MLOps Engineer II</t>
+          <t>Senior Engineer, Software Development Test QE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Spark, PySpark, SQL Server, MySQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dae99e1ea457637a</t>
+          <t>https://www.indeed.com/viewjob?jk=56447c16c3ba977a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Software Engineer - CostCheck</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Intellivo</t>
+          <t>BlueSight</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Athena, S3, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a247e4c9f8838e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b724f0ef5f1675</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Gen AI Architect</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>QualityAI</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6f26d72223ee99</t>
+          <t>https://www.indeed.com/viewjob?jk=f587f9ae6e2cdaae</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer Specialists</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>MediaRadar</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Oracle, PostgreSQL, DynamoDB, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, SQL Server, ETL, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e65c0f51719bda</t>
+          <t>https://www.indeed.com/viewjob?jk=180b2fb1ba9c363d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6sense</t>
+          <t>NFI Industries</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05703cc8519b448f</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9c3d571174ee0c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate Dir, Full Stack Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5df2a862bf9db8</t>
+          <t>https://www.indeed.com/viewjob?jk=602b89794c6d97b1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f5d55a58f8c38c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a86f04695064d5c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - DevOps</t>
+          <t>Senior Platform Engineer – Database Administration (AWS Focus)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ADG Tech Consulting</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, PostgreSQL, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9b07407edcc90ef</t>
+          <t>https://www.indeed.com/viewjob?jk=8a8c07785abe3a74</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior AI Engineer 2026 - US</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cfca332d489410</t>
+          <t>https://www.indeed.com/viewjob?jk=13884b1c57640398</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development Test QE</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, SQL Server, MySQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56447c16c3ba977a</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ba93b8542af918</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - CostCheck</t>
+          <t>Senior Product Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BlueSight</t>
+          <t>Ticket Takedown LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, Maven</t>
+          <t>BigQuery, Scala, NoSQL, Data Modeling, Docker, pytest, Airflow, Apache Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,112 +2526,112 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b724f0ef5f1675</t>
+          <t>https://www.indeed.com/viewjob?jk=55148fbc10cb871e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>IOS Developer + Node.js</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>SIGNITIVES</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>EMR, RDS, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f587f9ae6e2cdaae</t>
+          <t>https://www.indeed.com/viewjob?jk=5fe2db57addb7567</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, NoSQL, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46176023248faed5</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdbca4cb9ae66f3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MediaRadar</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, SQL Server, ETL, dbt, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180b2fb1ba9c363d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2bbd584cafb766</t>
         </is>
       </c>
     </row>
@@ -2643,20 +2643,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,137 +2666,137 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9c3d571174ee0c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f49ef023c8c96de</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer - International Project</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=602b89794c6d97b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e71d6f8a3530ffa9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Software Engineer, Pipeline</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Flock Safety</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, DynamoDB, ELT, Maven, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a86f04695064d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=af3cae7b79ecbc73</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior AI Engineer 2026 - US</t>
+          <t>Senior Software Engineer, Pipeline</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Flock</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, DynamoDB, ELT, Maven, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13884b1c57640398</t>
+          <t>https://www.indeed.com/viewjob?jk=1419caf3acf86f5e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ba93b8542af918</t>
+          <t>https://www.indeed.com/viewjob?jk=2e8a0f3adb10969c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073dcbe12166b408</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d641f8b88bb4c</t>
         </is>
       </c>
     </row>
@@ -2853,20 +2853,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PostgreSQL, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5283a1c7f91253d8</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c582c80db561b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Search Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,94 +2911,94 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b805c6c3ef2ef74</t>
+          <t>https://www.indeed.com/viewjob?jk=796a5092268ae3dc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IOS Developer + Node.js</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SIGNITIVES</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>EMR, RDS, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fe2db57addb7567</t>
+          <t>https://www.indeed.com/viewjob?jk=99dcfa53429fedf3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Product Engineer</t>
+          <t>Senior Platform Engineer, Data &amp; AI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ticket Takedown LLC</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>BigQuery, Scala, NoSQL, Data Modeling, Docker, pytest, Airflow, Apache Airflow, Git, Python</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55148fbc10cb871e</t>
+          <t>https://www.indeed.com/viewjob?jk=f70e3e5b69eb2b62</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Sr Automation Engineer Sales</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Raya Workforce</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Woodstock, VT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,427 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdbca4cb9ae66f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - Databricks</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>SugarAI</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2bbd584cafb766</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f49ef023c8c96de</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>DevOps Engineer - International Project</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e71d6f8a3530ffa9</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior Java Developer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c51ea63d2c9240e</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Empirx Health</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d641f8b88bb4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer - US</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>GreenBox Capital</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0eba562e0eef18</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer, Data &amp; AI</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>National Debt Relief</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f70e3e5b69eb2b62</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Sr Automation Engineer Sales</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Raya Workforce</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Woodstock, VT, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=21e43ea584d339bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Machine Learning Intern</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Aivra Health</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e8a0f3adb10969c</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Magnet Forensics</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PostgreSQL, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c582c80db561b</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=796a5092268ae3dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Bridgewater, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99dcfa53429fedf3</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-30.xlsx
+++ b/results/job_matches_2026-06-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Big Data &amp; MCP, Data Foundations</t>
+          <t>Database Engineer - SQL &amp; Oracle PL/SQL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e6bda7c4edc743</t>
+          <t>https://www.indeed.com/viewjob?jk=fd734f22170030b0</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c603d89b037c27ac</t>
+          <t>https://www.indeed.com/viewjob?jk=12e6bda7c4edc743</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Engineer</t>
+          <t>Senior Software Engineer- Big Data &amp; MCP, Data Foundations</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805d9159d3aff63f</t>
+          <t>https://www.indeed.com/viewjob?jk=c603d89b037c27ac</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior IT Big Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Willdan</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,42 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8020391c43706e33</t>
+          <t>https://www.indeed.com/viewjob?jk=805d9159d3aff63f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L1)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de33f3f460768669</t>
+          <t>https://www.indeed.com/viewjob?jk=8020391c43706e33</t>
         </is>
       </c>
     </row>
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a58fca26aa0b565</t>
+          <t>https://www.indeed.com/viewjob?jk=de33f3f460768669</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Data (L1)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5f1d848e75885</t>
+          <t>https://www.indeed.com/viewjob?jk=5a58fca26aa0b565</t>
         </is>
       </c>
     </row>
@@ -1168,25 +1168,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III - Visual AI Technology</t>
+          <t>Data Engineer III, Development</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bb194dac269cfc4</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f5ff112c1e4fbb</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer III, Development</t>
+          <t>AWS Databricks Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Solvstaff</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark, Kafka</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f5ff112c1e4fbb</t>
+          <t>https://www.indeed.com/viewjob?jk=5a9a04b047de59e9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Associate Data Engineer / Data Engineer II / Senior Data Engineer (REMOTE)</t>
+          <t>Senior Full-Stack Software Engineer – Back-End Focused</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>STAND TOGETHER</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=665858153a76bc87</t>
+          <t>https://www.indeed.com/viewjob?jk=27c394a83edfce01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Databricks Platform &amp; Data Engineer</t>
+          <t>Senior Backend Engineer, Core APIs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Fingerprint</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4b537ec115b25d9</t>
+          <t>https://www.indeed.com/viewjob?jk=89f151cbc6d5b613</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS Databricks Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Solvstaff</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a9a04b047de59e9</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0c72a3fb65e08</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer – Back-End Focused</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>STAND TOGETHER</t>
+          <t>Western Alliance Bank</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c394a83edfce01</t>
+          <t>https://www.indeed.com/viewjob?jk=34c193d803b2a019</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIs</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fingerprint</t>
+          <t>Fracht Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89f151cbc6d5b613</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa96d3d36ceb7ae</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Western Alliance Bank</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, Snowflake, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c193d803b2a019</t>
+          <t>https://www.indeed.com/viewjob?jk=675596684c392e8e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect (P4642)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fracht Group</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa96d3d36ceb7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=1660a4cf0a8045d0</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1660a4cf0a8045d0</t>
+          <t>https://www.indeed.com/viewjob?jk=39b5a4b6b25e561f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Architect (P4642)</t>
+          <t>Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39b5a4b6b25e561f</t>
+          <t>https://www.indeed.com/viewjob?jk=2048b8f9fc33e871</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer II (US)</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2048b8f9fc33e871</t>
+          <t>https://www.indeed.com/viewjob?jk=a78649b3c052ca64</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Databricks, Blob Storage, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0c72a3fb65e08</t>
+          <t>https://www.indeed.com/viewjob?jk=ac49aa80fd785089</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Union City, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac49aa80fd785089</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d63ab0e4452de4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Union City, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,104 +1711,104 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d63ab0e4452de4</t>
+          <t>https://www.indeed.com/viewjob?jk=a0ead42f0db52dd0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, S3, RDS, Databricks, Unity Catalog, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0ead42f0db52dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=e4db27c4a07cdc78</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>MLOps Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675596684c392e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=dae99e1ea457637a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Gen AI Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>QualityAI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Databricks, Unity Catalog, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4db27c4a07cdc78</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6f26d72223ee99</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MLOps Engineer II</t>
+          <t>DevOps Software Engineer Specialists</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Oracle, PostgreSQL, DynamoDB, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dae99e1ea457637a</t>
+          <t>https://www.indeed.com/viewjob?jk=06e65c0f51719bda</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Gen AI Architect</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>QualityAI</t>
+          <t>6sense</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6f26d72223ee99</t>
+          <t>https://www.indeed.com/viewjob?jk=05703cc8519b448f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer Specialists</t>
+          <t>Expert Analyst Data Management (Epic ODBA Cert Req'd)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Oracle, PostgreSQL, DynamoDB, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e65c0f51719bda</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4bf16bfeb52f1c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr BI Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6sense</t>
+          <t>Cherokee Nation Businesses</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Catoosa, OK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05703cc8519b448f</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ec894200ccbed7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Expert Analyst Data Management (Epic ODBA Cert Req'd)</t>
+          <t>Sr. Software Engineer - AI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
+          <t>LogicMonitor</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Terraform</t>
+          <t>RDS, Spark, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,59 +2001,59 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4bf16bfeb52f1c</t>
+          <t>https://www.indeed.com/viewjob?jk=951fb41e37160d69</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Associate Dir, Full Stack Data Scientist</t>
+          <t>Senior Data Engineer - DevOps</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>ADG Tech Consulting</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5df2a862bf9db8</t>
+          <t>https://www.indeed.com/viewjob?jk=e9b07407edcc90ef</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI</t>
+          <t>Senior Engineer, Software Development Test QE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LogicMonitor</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, S3, RDS, Spark, PySpark, SQL Server, MySQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951fb41e37160d69</t>
+          <t>https://www.indeed.com/viewjob?jk=56447c16c3ba977a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - DevOps</t>
+          <t>Senior Full Stack Software Engineer - CostCheck</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ADG Tech Consulting</t>
+          <t>BlueSight</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Athena, S3, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9b07407edcc90ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b724f0ef5f1675</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cfca332d489410</t>
+          <t>https://www.indeed.com/viewjob?jk=f587f9ae6e2cdaae</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Development Test QE</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, SQL Server, MySQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56447c16c3ba977a</t>
+          <t>https://www.indeed.com/viewjob?jk=64cfca332d489410</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - CostCheck</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BlueSight</t>
+          <t>MediaRadar</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, SQL Server, ETL, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b724f0ef5f1675</t>
+          <t>https://www.indeed.com/viewjob?jk=180b2fb1ba9c363d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>NFI Industries</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f587f9ae6e2cdaae</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9c3d571174ee0c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Security &amp; DevSecOps Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MediaRadar</t>
+          <t>Medical Mutual of Ohio</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, SQL Server, ETL, dbt, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180b2fb1ba9c363d</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf4cefc84dbe107</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>Crunchyroll</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, CI/CD, CloudWatch, Datadog</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9c3d571174ee0c</t>
+          <t>https://www.indeed.com/viewjob?jk=af01fcb1c7730c1d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer – Database Administration (AWS Focus)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, PostgreSQL, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=602b89794c6d97b1</t>
+          <t>https://www.indeed.com/viewjob?jk=8a8c07785abe3a74</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior AI Engineer 2026 - US</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a86f04695064d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=13884b1c57640398</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Database Administration (AWS Focus)</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, PostgreSQL, CI/CD, Terraform, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a8c07785abe3a74</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ba93b8542af918</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior AI Engineer 2026 - US</t>
+          <t>IOS Developer + Node.js</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>SIGNITIVES</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,112 +2446,112 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
+          <t>EMR, RDS, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13884b1c57640398</t>
+          <t>https://www.indeed.com/viewjob?jk=5fe2db57addb7567</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ba93b8542af918</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2bbd584cafb766</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Product Engineer</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ticket Takedown LLC</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>BigQuery, Scala, NoSQL, Data Modeling, Docker, pytest, Airflow, Apache Airflow, Git, Python</t>
+          <t>AWS, Lambda, S3, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55148fbc10cb871e</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdbca4cb9ae66f3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>IOS Developer + Node.js</t>
+          <t>DevOps Engineer - International Project</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SIGNITIVES</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>EMR, RDS, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fe2db57addb7567</t>
+          <t>https://www.indeed.com/viewjob?jk=e71d6f8a3530ffa9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Senior Software Engineer, Pipeline</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Flock Safety</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, MySQL, CI/CD, Terraform, Docker, Git</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, DynamoDB, ELT, Maven, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdbca4cb9ae66f3</t>
+          <t>https://www.indeed.com/viewjob?jk=af3cae7b79ecbc73</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Senior Software Engineer, Pipeline</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>Flock</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, DynamoDB, ELT, Maven, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2bbd584cafb766</t>
+          <t>https://www.indeed.com/viewjob?jk=1419caf3acf86f5e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f49ef023c8c96de</t>
+          <t>https://www.indeed.com/viewjob?jk=2e8a0f3adb10969c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps Engineer - International Project</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e71d6f8a3530ffa9</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d641f8b88bb4c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Pipeline</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Flock Safety</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,29 +2726,29 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, DynamoDB, ELT, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Spark, PostgreSQL, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af3cae7b79ecbc73</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c582c80db561b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Pipeline</t>
+          <t>Senior Platform Engineer, Data &amp; AI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Flock</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,262 +2761,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, PostgreSQL, DynamoDB, ELT, Maven, Docker</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1419caf3acf86f5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Machine Learning Intern</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Aivra Health</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e8a0f3adb10969c</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Empirx Health</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d641f8b88bb4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Magnet Forensics</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PostgreSQL, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c582c80db561b</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=796a5092268ae3dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Bridgewater, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99dcfa53429fedf3</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer, Data &amp; AI</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>National Debt Relief</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=f70e3e5b69eb2b62</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Sr Automation Engineer Sales</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Raya Workforce</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Woodstock, VT, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Snowflake, DynamoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21e43ea584d339bf</t>
         </is>
       </c>
     </row>
